--- a/Master-data.xlsx
+++ b/Master-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\0WorkingOn\Sonny-DAX\Module2 Data Analysis Expression(DAX)\Project2Majestic Traders Kings of Import and Export\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F6195F-EE30-4427-9FD8-5FB0AC34877E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD574C9-D257-4FC8-891C-0CA3205EAFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5328" yWindow="1452" windowWidth="24156" windowHeight="15396" activeTab="2" xr2:uid="{CD89F825-D4DA-4AD5-A4C0-5046E380910E}"/>
+    <workbookView xWindow="4116" yWindow="1596" windowWidth="24000" windowHeight="13272" activeTab="2" xr2:uid="{CD89F825-D4DA-4AD5-A4C0-5046E380910E}"/>
   </bookViews>
   <sheets>
     <sheet name="Categories" sheetId="1" r:id="rId1"/>
@@ -6909,7 +6909,7 @@
         <v>39</v>
       </c>
       <c r="H2" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2">
         <v>10</v>
@@ -7013,12 +7013,8 @@
       <c r="G5" s="2">
         <v>53</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
       <c r="J5" s="3" t="s">
         <v>769</v>
       </c>
@@ -7045,15 +7041,9 @@
       <c r="F6" s="1">
         <v>21.35</v>
       </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
         <v>778</v>
       </c>
@@ -7083,9 +7073,7 @@
       <c r="G7" s="2">
         <v>120</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="2">
         <v>25</v>
       </c>
@@ -7118,9 +7106,7 @@
       <c r="G8" s="2">
         <v>15</v>
       </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2">
         <v>10</v>
       </c>
@@ -7153,12 +7139,8 @@
       <c r="G9" s="2">
         <v>6</v>
       </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="3" t="s">
         <v>769</v>
       </c>
@@ -7188,12 +7170,8 @@
       <c r="G10" s="2">
         <v>29</v>
       </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="3" t="s">
         <v>778</v>
       </c>
@@ -7223,12 +7201,8 @@
       <c r="G11" s="2">
         <v>31</v>
       </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="3" t="s">
         <v>769</v>
       </c>
@@ -7293,12 +7267,8 @@
       <c r="G13" s="2">
         <v>86</v>
       </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="3" t="s">
         <v>769</v>
       </c>
@@ -7328,9 +7298,7 @@
       <c r="G14" s="2">
         <v>24</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
+      <c r="H14" s="2"/>
       <c r="I14" s="2">
         <v>5</v>
       </c>
@@ -7363,12 +7331,8 @@
       <c r="G15" s="2">
         <v>35</v>
       </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
       <c r="J15" s="3" t="s">
         <v>769</v>
       </c>
@@ -7398,9 +7362,7 @@
       <c r="G16" s="2">
         <v>39</v>
       </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2">
         <v>5</v>
       </c>
@@ -7433,9 +7395,7 @@
       <c r="G17" s="2">
         <v>29</v>
       </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
+      <c r="H17" s="2"/>
       <c r="I17" s="2">
         <v>10</v>
       </c>
@@ -7465,15 +7425,9 @@
       <c r="F18" s="1">
         <v>39</v>
       </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
       <c r="J18" s="3" t="s">
         <v>778</v>
       </c>
@@ -7503,12 +7457,8 @@
       <c r="G19" s="2">
         <v>42</v>
       </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
       <c r="J19" s="3" t="s">
         <v>769</v>
       </c>
@@ -7538,9 +7488,7 @@
       <c r="G20" s="2">
         <v>25</v>
       </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
+      <c r="H20" s="2"/>
       <c r="I20" s="2">
         <v>5</v>
       </c>
@@ -7573,12 +7521,8 @@
       <c r="G21" s="2">
         <v>40</v>
       </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
       <c r="J21" s="3" t="s">
         <v>769</v>
       </c>
@@ -7643,9 +7587,7 @@
       <c r="G23" s="2">
         <v>104</v>
       </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
+      <c r="H23" s="2"/>
       <c r="I23" s="2">
         <v>25</v>
       </c>
@@ -7678,9 +7620,7 @@
       <c r="G24" s="2">
         <v>61</v>
       </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
+      <c r="H24" s="2"/>
       <c r="I24" s="2">
         <v>25</v>
       </c>
@@ -7713,12 +7653,8 @@
       <c r="G25" s="2">
         <v>20</v>
       </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
       <c r="J25" s="3" t="s">
         <v>778</v>
       </c>
@@ -7748,9 +7684,7 @@
       <c r="G26" s="2">
         <v>76</v>
       </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
+      <c r="H26" s="2"/>
       <c r="I26" s="2">
         <v>30</v>
       </c>
@@ -7783,12 +7717,8 @@
       <c r="G27" s="2">
         <v>15</v>
       </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="3" t="s">
         <v>769</v>
       </c>
@@ -7818,9 +7748,7 @@
       <c r="G28" s="2">
         <v>49</v>
       </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
+      <c r="H28" s="2"/>
       <c r="I28" s="2">
         <v>30</v>
       </c>
@@ -7853,12 +7781,8 @@
       <c r="G29" s="2">
         <v>26</v>
       </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
       <c r="J29" s="3" t="s">
         <v>778</v>
       </c>
@@ -7885,15 +7809,9 @@
       <c r="F30" s="1">
         <v>123.79</v>
       </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
       <c r="J30" s="3" t="s">
         <v>778</v>
       </c>
@@ -7923,9 +7841,7 @@
       <c r="G31" s="2">
         <v>10</v>
       </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
+      <c r="H31" s="2"/>
       <c r="I31" s="2">
         <v>15</v>
       </c>
@@ -7955,9 +7871,7 @@
       <c r="F32" s="1">
         <v>12.5</v>
       </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
+      <c r="G32" s="2"/>
       <c r="H32" s="2">
         <v>70</v>
       </c>
@@ -8028,9 +7942,7 @@
       <c r="G34" s="2">
         <v>112</v>
       </c>
-      <c r="H34" s="2">
-        <v>0</v>
-      </c>
+      <c r="H34" s="2"/>
       <c r="I34" s="2">
         <v>20</v>
       </c>
@@ -8063,9 +7975,7 @@
       <c r="G35" s="2">
         <v>111</v>
       </c>
-      <c r="H35" s="2">
-        <v>0</v>
-      </c>
+      <c r="H35" s="2"/>
       <c r="I35" s="2">
         <v>15</v>
       </c>
@@ -8098,9 +8008,7 @@
       <c r="G36" s="2">
         <v>20</v>
       </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
+      <c r="H36" s="2"/>
       <c r="I36" s="2">
         <v>15</v>
       </c>
@@ -8133,9 +8041,7 @@
       <c r="G37" s="2">
         <v>112</v>
       </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
+      <c r="H37" s="2"/>
       <c r="I37" s="2">
         <v>20</v>
       </c>
@@ -8203,9 +8109,7 @@
       <c r="G39" s="2">
         <v>17</v>
       </c>
-      <c r="H39" s="2">
-        <v>0</v>
-      </c>
+      <c r="H39" s="2"/>
       <c r="I39" s="2">
         <v>15</v>
       </c>
@@ -8238,9 +8142,7 @@
       <c r="G40" s="2">
         <v>69</v>
       </c>
-      <c r="H40" s="2">
-        <v>0</v>
-      </c>
+      <c r="H40" s="2"/>
       <c r="I40" s="2">
         <v>5</v>
       </c>
@@ -8273,9 +8175,7 @@
       <c r="G41" s="2">
         <v>123</v>
       </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
+      <c r="H41" s="2"/>
       <c r="I41" s="2">
         <v>30</v>
       </c>
@@ -8308,9 +8208,7 @@
       <c r="G42" s="2">
         <v>85</v>
       </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="2">
         <v>10</v>
       </c>
@@ -8343,12 +8241,8 @@
       <c r="G43" s="2">
         <v>26</v>
       </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
       <c r="J43" s="3" t="s">
         <v>778</v>
       </c>
@@ -8413,9 +8307,7 @@
       <c r="G45" s="2">
         <v>27</v>
       </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
+      <c r="H45" s="2"/>
       <c r="I45" s="2">
         <v>15</v>
       </c>
@@ -8483,12 +8375,8 @@
       <c r="G47" s="2">
         <v>95</v>
       </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
       <c r="J47" s="3" t="s">
         <v>769</v>
       </c>
@@ -8518,12 +8406,8 @@
       <c r="G48" s="2">
         <v>36</v>
       </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
       <c r="J48" s="3" t="s">
         <v>769</v>
       </c>
@@ -8623,9 +8507,7 @@
       <c r="G51" s="2">
         <v>65</v>
       </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
+      <c r="H51" s="2"/>
       <c r="I51" s="2">
         <v>30</v>
       </c>
@@ -8658,9 +8540,7 @@
       <c r="G52" s="2">
         <v>20</v>
       </c>
-      <c r="H52" s="2">
-        <v>0</v>
-      </c>
+      <c r="H52" s="2"/>
       <c r="I52" s="2">
         <v>10</v>
       </c>
@@ -8693,9 +8573,7 @@
       <c r="G53" s="2">
         <v>38</v>
       </c>
-      <c r="H53" s="2">
-        <v>0</v>
-      </c>
+      <c r="H53" s="2"/>
       <c r="I53" s="2">
         <v>25</v>
       </c>
@@ -8725,15 +8603,9 @@
       <c r="F54" s="1">
         <v>32.799999999999997</v>
       </c>
-      <c r="G54" s="2">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
       <c r="J54" s="3" t="s">
         <v>778</v>
       </c>
@@ -8763,9 +8635,7 @@
       <c r="G55" s="2">
         <v>21</v>
       </c>
-      <c r="H55" s="2">
-        <v>0</v>
-      </c>
+      <c r="H55" s="2"/>
       <c r="I55" s="2">
         <v>10</v>
       </c>
@@ -8798,9 +8668,7 @@
       <c r="G56" s="2">
         <v>115</v>
       </c>
-      <c r="H56" s="2">
-        <v>0</v>
-      </c>
+      <c r="H56" s="2"/>
       <c r="I56" s="2">
         <v>20</v>
       </c>
@@ -8868,9 +8736,7 @@
       <c r="G58" s="2">
         <v>36</v>
       </c>
-      <c r="H58" s="2">
-        <v>0</v>
-      </c>
+      <c r="H58" s="2"/>
       <c r="I58" s="2">
         <v>20</v>
       </c>
@@ -8903,9 +8769,7 @@
       <c r="G59" s="2">
         <v>62</v>
       </c>
-      <c r="H59" s="2">
-        <v>0</v>
-      </c>
+      <c r="H59" s="2"/>
       <c r="I59" s="2">
         <v>20</v>
       </c>
@@ -8938,12 +8802,8 @@
       <c r="G60" s="2">
         <v>79</v>
       </c>
-      <c r="H60" s="2">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
       <c r="J60" s="3" t="s">
         <v>769</v>
       </c>
@@ -8973,12 +8833,8 @@
       <c r="G61" s="2">
         <v>19</v>
       </c>
-      <c r="H61" s="2">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
       <c r="J61" s="3" t="s">
         <v>769</v>
       </c>
@@ -9008,9 +8864,7 @@
       <c r="G62" s="2">
         <v>113</v>
       </c>
-      <c r="H62" s="2">
-        <v>0</v>
-      </c>
+      <c r="H62" s="2"/>
       <c r="I62" s="2">
         <v>25</v>
       </c>
@@ -9043,12 +8897,8 @@
       <c r="G63" s="2">
         <v>17</v>
       </c>
-      <c r="H63" s="2">
-        <v>0</v>
-      </c>
-      <c r="I63" s="2">
-        <v>0</v>
-      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
       <c r="J63" s="3" t="s">
         <v>769</v>
       </c>
@@ -9078,9 +8928,7 @@
       <c r="G64" s="2">
         <v>24</v>
       </c>
-      <c r="H64" s="2">
-        <v>0</v>
-      </c>
+      <c r="H64" s="2"/>
       <c r="I64" s="2">
         <v>5</v>
       </c>
@@ -9148,12 +8996,8 @@
       <c r="G66" s="2">
         <v>76</v>
       </c>
-      <c r="H66" s="2">
-        <v>0</v>
-      </c>
-      <c r="I66" s="2">
-        <v>0</v>
-      </c>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
       <c r="J66" s="3" t="s">
         <v>769</v>
       </c>
@@ -9218,9 +9062,7 @@
       <c r="G68" s="2">
         <v>52</v>
       </c>
-      <c r="H68" s="2">
-        <v>0</v>
-      </c>
+      <c r="H68" s="2"/>
       <c r="I68" s="2">
         <v>10</v>
       </c>
@@ -9288,9 +9130,7 @@
       <c r="G70" s="2">
         <v>26</v>
       </c>
-      <c r="H70" s="2">
-        <v>0</v>
-      </c>
+      <c r="H70" s="2"/>
       <c r="I70" s="2">
         <v>15</v>
       </c>
@@ -9358,12 +9198,8 @@
       <c r="G72" s="2">
         <v>26</v>
       </c>
-      <c r="H72" s="2">
-        <v>0</v>
-      </c>
-      <c r="I72" s="2">
-        <v>0</v>
-      </c>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
       <c r="J72" s="3" t="s">
         <v>769</v>
       </c>
@@ -9393,12 +9229,8 @@
       <c r="G73" s="2">
         <v>14</v>
       </c>
-      <c r="H73" s="2">
-        <v>0</v>
-      </c>
-      <c r="I73" s="2">
-        <v>0</v>
-      </c>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
       <c r="J73" s="3" t="s">
         <v>769</v>
       </c>
@@ -9428,9 +9260,7 @@
       <c r="G74" s="2">
         <v>101</v>
       </c>
-      <c r="H74" s="2">
-        <v>0</v>
-      </c>
+      <c r="H74" s="2"/>
       <c r="I74" s="2">
         <v>5</v>
       </c>
@@ -9498,9 +9328,7 @@
       <c r="G76" s="2">
         <v>125</v>
       </c>
-      <c r="H76" s="2">
-        <v>0</v>
-      </c>
+      <c r="H76" s="2"/>
       <c r="I76" s="2">
         <v>25</v>
       </c>
@@ -9533,9 +9361,7 @@
       <c r="G77" s="2">
         <v>57</v>
       </c>
-      <c r="H77" s="2">
-        <v>0</v>
-      </c>
+      <c r="H77" s="2"/>
       <c r="I77" s="2">
         <v>20</v>
       </c>
@@ -9568,9 +9394,7 @@
       <c r="G78" s="2">
         <v>32</v>
       </c>
-      <c r="H78" s="2">
-        <v>0</v>
-      </c>
+      <c r="H78" s="2"/>
       <c r="I78" s="2">
         <v>15</v>
       </c>
